--- a/dados/excel/secretaria_tempo.xlsx
+++ b/dados/excel/secretaria_tempo.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$E$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -810,13 +810,13 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="11" t="n">
-        <v>20260.58</v>
+        <v>17497.36</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>20260.58</v>
+        <v>17617.8</v>
       </c>
     </row>
     <row r="3">
@@ -834,10 +834,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="15" t="n">
-        <v>10627.11</v>
+        <v>17301.37</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>10627.11</v>
+        <v>17301.37</v>
       </c>
     </row>
     <row r="4">
@@ -855,10 +855,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="11" t="n">
-        <v>18482.78</v>
+        <v>11053.06</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>18482.78</v>
+        <v>11053.06</v>
       </c>
     </row>
     <row r="5">
@@ -876,10 +876,10 @@
         <v>2</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>17931.76</v>
+        <v>21815.32</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>17931.76</v>
+        <v>21815.32</v>
       </c>
     </row>
     <row r="6">
@@ -981,7 +981,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>5670.21</v>
+        <v>5670.2</v>
       </c>
       <c r="E10" s="11" t="n">
         <v>4861.96</v>
@@ -1002,7 +1002,7 @@
         <v>19</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>5717.93</v>
+        <v>5723.69</v>
       </c>
       <c r="E11" s="15" t="n">
         <v>4745.33</v>
@@ -1023,7 +1023,7 @@
         <v>90</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>6465.57</v>
+        <v>6474.93</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>4819.49</v>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>7708.85</v>
+        <v>6718.06</v>
       </c>
       <c r="E13" s="15" t="n">
         <v>7150.18</v>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>8037.67</v>
+        <v>9079.719999999999</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>8557.309999999999</v>
+        <v>8364.68</v>
       </c>
     </row>
     <row r="15">
@@ -1086,10 +1086,10 @@
         <v>95</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>9520.940000000001</v>
+        <v>9745.77</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>9660.48</v>
+        <v>9801.07</v>
       </c>
     </row>
     <row r="16">
@@ -1107,10 +1107,10 @@
         <v>32</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>13214.91</v>
+        <v>13666.94</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>12224.24</v>
+        <v>12034.41</v>
       </c>
     </row>
     <row r="17">
@@ -1128,10 +1128,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>19530.26</v>
+        <v>20077.23</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>19530.26</v>
+        <v>20077.23</v>
       </c>
     </row>
     <row r="18">
@@ -1142,38 +1142,38 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D18" s="11" t="n">
-        <v>23864.44</v>
+        <v>8729.25</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>20829.1</v>
+        <v>8729.25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Educação</t>
+          <t>Secretaria da Cidadania</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>3272</v>
+        <v>8</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>4524</v>
+        <v>21374.08</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>3858.38</v>
+        <v>18027.64</v>
       </c>
     </row>
     <row r="20">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1448</v>
+        <v>3645</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>6593.8</v>
+        <v>4630.06</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>5509.59</v>
+        <v>3873.26</v>
       </c>
     </row>
     <row r="21">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1858</v>
+        <v>1556</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>8365.059999999999</v>
+        <v>6477.73</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>5931.56</v>
+        <v>5320.18</v>
       </c>
     </row>
     <row r="22">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>958</v>
+        <v>1893</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>11129.26</v>
+        <v>8478.809999999999</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>10888.64</v>
+        <v>5936.79</v>
       </c>
     </row>
     <row r="23">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>474</v>
+        <v>985</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>10991.72</v>
+        <v>11088.75</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>7801.74</v>
+        <v>10087.11</v>
       </c>
     </row>
     <row r="24">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>47</v>
+        <v>482</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>8795.76</v>
+        <v>10955.52</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>2050.4</v>
+        <v>7829.24</v>
       </c>
     </row>
     <row r="25">
@@ -1289,38 +1289,38 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>13248.7</v>
+        <v>9833.32</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>8062.27</v>
+        <v>2796</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Fazenda</t>
+          <t>Secretaria da Educação</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>7274.69</v>
+        <v>12322.18</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>5104.15</v>
+        <v>7745.15</v>
       </c>
     </row>
     <row r="27">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>9009.85</v>
+        <v>8129.26</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>6068.02</v>
+        <v>7060.9</v>
       </c>
     </row>
     <row r="28">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>11578.81</v>
+        <v>11695.06</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>8247.75</v>
+        <v>9632.030000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>17154.29</v>
+        <v>12362.85</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>16066.6</v>
+        <v>10997.26</v>
       </c>
     </row>
     <row r="30">
@@ -1394,17 +1394,17 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>6449.79</v>
+        <v>18948.99</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>6449.79</v>
+        <v>18430.28</v>
       </c>
     </row>
     <row r="31">
@@ -1415,38 +1415,38 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>20106.35</v>
+        <v>8870.530000000001</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>17965.07</v>
+        <v>8870.530000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Habitação e Regularização Fundiária</t>
+          <t>Secretaria da Fazenda</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>9560.4</v>
+        <v>22073.17</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>9571.76</v>
+        <v>19632.89</v>
       </c>
     </row>
     <row r="33">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>11815.66</v>
+        <v>10255.3</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>14092.07</v>
+        <v>10374.15</v>
       </c>
     </row>
     <row r="34">
@@ -1478,17 +1478,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>11178.35</v>
+        <v>10644.48</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>8774.01</v>
+        <v>9866.209999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1499,38 +1499,38 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
         <v>10</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>15344.3</v>
+        <v>10318.55</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>12238.15</v>
+        <v>6098.04</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Mulher</t>
+          <t>Secretaria da Habitação e Regularização Fundiária</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>16276.38</v>
+        <v>14560.35</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>15480.31</v>
+        <v>11871.38</v>
       </c>
     </row>
     <row r="37">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>14630.31</v>
+        <v>4549.47</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>14630.31</v>
+        <v>2894.39</v>
       </c>
     </row>
     <row r="38">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>12760.07</v>
+        <v>18689.96</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>12760.07</v>
+        <v>16870.38</v>
       </c>
     </row>
     <row r="39">
@@ -1583,59 +1583,59 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>17023.27</v>
+        <v>14869.47</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>17023.27</v>
+        <v>14869.47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="D40" s="11" t="n">
-        <v>8035.21</v>
+        <v>6212.68</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>6023.06</v>
+        <v>6212.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>8615.18</v>
+        <v>17111.33</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>5471.01</v>
+        <v>17111.33</v>
       </c>
     </row>
     <row r="42">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>803</v>
+        <v>931</v>
       </c>
       <c r="D42" s="11" t="n">
-        <v>10086.15</v>
+        <v>8009.87</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>7713.59</v>
+        <v>5941.41</v>
       </c>
     </row>
     <row r="43">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>587</v>
+        <v>233</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>14531.92</v>
+        <v>9373.139999999999</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>11143.97</v>
+        <v>6288.82</v>
       </c>
     </row>
     <row r="44">
@@ -1688,17 +1688,17 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>205</v>
+        <v>797</v>
       </c>
       <c r="D44" s="11" t="n">
-        <v>17954.01</v>
+        <v>10139.19</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>16412.76</v>
+        <v>7821.5</v>
       </c>
     </row>
     <row r="45">
@@ -1709,17 +1709,17 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>35</v>
+        <v>587</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>26197.82</v>
+        <v>14440.7</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>22427.41</v>
+        <v>11344.73</v>
       </c>
     </row>
     <row r="46">
@@ -1730,59 +1730,59 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="D46" s="11" t="n">
-        <v>17431.4</v>
+        <v>17508.17</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>16074.73</v>
+        <v>15543.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>4827.88</v>
+        <v>22212.58</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>4180.24</v>
+        <v>19532.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>9590.93</v>
+        <v>17871.6</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>6281.98</v>
+        <v>16436.34</v>
       </c>
     </row>
     <row r="49">
@@ -1793,17 +1793,17 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>11641.11</v>
+        <v>4640.2</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>11443.85</v>
+        <v>4371.93</v>
       </c>
     </row>
     <row r="50">
@@ -1814,17 +1814,17 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D50" s="11" t="n">
-        <v>15086.19</v>
+        <v>11121.51</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>12083.4</v>
+        <v>6894.15</v>
       </c>
     </row>
     <row r="51">
@@ -1835,59 +1835,59 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>9092.16</v>
+        <v>12582.24</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>8590.99</v>
+        <v>11368.45</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="D52" s="11" t="n">
-        <v>13114.96</v>
+        <v>14276.84</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>4728.34</v>
+        <v>12821.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>21013.39</v>
+        <v>10219.2</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>13002.28</v>
+        <v>8982.469999999999</v>
       </c>
     </row>
     <row r="54">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="D54" s="11" t="n">
-        <v>17778.9</v>
+        <v>12822.18</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>12047.68</v>
+        <v>5111.51</v>
       </c>
     </row>
     <row r="55">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>25468.36</v>
+        <v>23715.03</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>14280.14</v>
+        <v>15644.94</v>
       </c>
     </row>
     <row r="56">
@@ -1940,59 +1940,59 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D56" s="11" t="n">
-        <v>50044.71</v>
+        <v>18132.8</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>50044.71</v>
+        <v>11957.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>9443.059999999999</v>
+        <v>23755.98</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>7374.61</v>
+        <v>14359.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D58" s="11" t="n">
-        <v>11835.75</v>
+        <v>51415.71</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>11874.93</v>
+        <v>51415.71</v>
       </c>
     </row>
     <row r="59">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D59" s="15" t="n">
-        <v>11863.16</v>
+        <v>8284.23</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>12689.8</v>
+        <v>7153.74</v>
       </c>
     </row>
     <row r="60">
@@ -2024,59 +2024,59 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D60" s="11" t="n">
-        <v>14430.92</v>
+        <v>14693.03</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>13831.31</v>
+        <v>13836.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D61" s="15" t="n">
-        <v>6489.21</v>
+        <v>16509.26</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>4638.58</v>
+        <v>13927.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>7641.81</v>
+        <v>13911.72</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1084.8</v>
+        <v>14488.81</v>
       </c>
     </row>
     <row r="63">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D63" s="15" t="n">
-        <v>7909.56</v>
+        <v>5540.02</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>6070.47</v>
+        <v>4422.34</v>
       </c>
     </row>
     <row r="64">
@@ -2108,17 +2108,17 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>9078.23</v>
+        <v>4170.75</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>5925.83</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="65">
@@ -2129,59 +2129,59 @@
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D65" s="15" t="n">
-        <v>8459.530000000001</v>
+        <v>9340.1</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>6859.25</v>
+        <v>8244.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>8007.48</v>
+        <v>13077.38</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>2478.37</v>
+        <v>10264.51</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C67" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D67" s="15" t="n">
-        <v>8965.83</v>
+        <v>8690.530000000001</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>10032.85</v>
+        <v>6576.09</v>
       </c>
     </row>
     <row r="68">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>29083.09</v>
+        <v>3509.82</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>29083.09</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="69">
@@ -2213,59 +2213,59 @@
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C69" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D69" s="15" t="n">
-        <v>14573.64</v>
+        <v>13957.48</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>14615.08</v>
+        <v>13619.85</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>9601.91</v>
+        <v>19243.55</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>4575.66</v>
+        <v>19243.55</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C71" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D71" s="15" t="n">
-        <v>11078.17</v>
+        <v>15419.43</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>11515.07</v>
+        <v>15962.99</v>
       </c>
     </row>
     <row r="72">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>7781.45</v>
+        <v>10262.29</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>5647.31</v>
+        <v>9748.73</v>
       </c>
     </row>
     <row r="73">
@@ -2297,59 +2297,59 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D73" s="15" t="n">
-        <v>11920.48</v>
+        <v>7339.68</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>10049.45</v>
+        <v>7228.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>7066.51</v>
+        <v>7280.98</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>6409.81</v>
+        <v>5228.05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D75" s="15" t="n">
-        <v>7468.33</v>
+        <v>9888.17</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>7014.85</v>
+        <v>9427.959999999999</v>
       </c>
     </row>
     <row r="76">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>9937.77</v>
+        <v>7069.44</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>8248.15</v>
+        <v>6815.76</v>
       </c>
     </row>
     <row r="77">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D77" s="15" t="n">
-        <v>13719.57</v>
+        <v>7843.15</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>13152.28</v>
+        <v>6932.68</v>
       </c>
     </row>
     <row r="78">
@@ -2402,59 +2402,59 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>18672.94</v>
+        <v>10356.79</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>21007.94</v>
+        <v>9451.219999999999</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="D79" s="15" t="n">
-        <v>6091.78</v>
+        <v>13137</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>5487.95</v>
+        <v>12641.21</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>8302.75</v>
+        <v>16717.7</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>6851.74</v>
+        <v>17499.63</v>
       </c>
     </row>
     <row r="81">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D81" s="15" t="n">
-        <v>12179.47</v>
+        <v>6010.28</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>11439.44</v>
+        <v>4422.34</v>
       </c>
     </row>
     <row r="82">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>15571.29</v>
+        <v>9683.870000000001</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>15818.46</v>
+        <v>7636.47</v>
       </c>
     </row>
     <row r="83">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="D83" s="15" t="n">
-        <v>26352.38</v>
+        <v>12438.69</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>26352.38</v>
+        <v>11048.65</v>
       </c>
     </row>
     <row r="84">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>25590.1</v>
+        <v>15502.47</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>25590.1</v>
+        <v>13038.55</v>
       </c>
     </row>
     <row r="85">
@@ -2549,59 +2549,59 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D85" s="15" t="n">
-        <v>28252.06</v>
+        <v>25227.85</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>23937.5</v>
+        <v>25227.85</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>10035.36</v>
+        <v>25590.08</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>8441.129999999999</v>
+        <v>25590.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C87" s="14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D87" s="15" t="n">
-        <v>8353.57</v>
+        <v>35221.25</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>8830.67</v>
+        <v>36966.91</v>
       </c>
     </row>
     <row r="88">
@@ -2612,17 +2612,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>17286.89</v>
+        <v>9437</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>15666.52</v>
+        <v>7127.23</v>
       </c>
     </row>
     <row r="89">
@@ -2633,17 +2633,17 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C89" s="14" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D89" s="15" t="n">
-        <v>15139.78</v>
+        <v>10686.25</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>15080.87</v>
+        <v>9294.9</v>
       </c>
     </row>
     <row r="90">
@@ -2654,17 +2654,17 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>24196.95</v>
+        <v>19580.32</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>24196.95</v>
+        <v>15639</v>
       </c>
     </row>
     <row r="91">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D91" s="15" t="n">
-        <v>11965.01</v>
+        <v>14108.15</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>11965.01</v>
+        <v>12715.11</v>
       </c>
     </row>
     <row r="92">
@@ -2696,59 +2696,59 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>24991.69</v>
+        <v>18811.81</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>24991.69</v>
+        <v>18811.81</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C93" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D93" s="15" t="n">
-        <v>9965.08</v>
+        <v>15598.94</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>9965.08</v>
+        <v>15598.94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>14719.81</v>
+        <v>23081.9</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>12179.75</v>
+        <v>23081.9</v>
       </c>
     </row>
     <row r="95">
@@ -2759,59 +2759,59 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D95" s="15" t="n">
-        <v>12997.37</v>
+        <v>9247.889999999999</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>11932.33</v>
+        <v>8019.91</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>6357.14</v>
+        <v>11068.13</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>5050.32</v>
+        <v>11303.44</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C97" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" s="15" t="n">
-        <v>1825.61</v>
+        <v>13652.25</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>1084.8</v>
+        <v>13952.01</v>
       </c>
     </row>
     <row r="98">
@@ -2822,17 +2822,17 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>9652.76</v>
+        <v>6205.52</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>12085.13</v>
+        <v>4724.26</v>
       </c>
     </row>
     <row r="99">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C99" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D99" s="15" t="n">
-        <v>15967.39</v>
+        <v>2562.45</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>14871.5</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="100">
@@ -2864,17 +2864,17 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>9101.17</v>
+        <v>10235.13</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>9101.17</v>
+        <v>12085.13</v>
       </c>
     </row>
     <row r="101">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C101" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D101" s="15" t="n">
-        <v>15794.57</v>
+        <v>15700.25</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>14904.24</v>
+        <v>14633.64</v>
       </c>
     </row>
     <row r="102">
@@ -2906,59 +2906,59 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>15628.57</v>
+        <v>14492.28</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>17712.49</v>
+        <v>14492.28</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C103" s="14" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D103" s="15" t="n">
-        <v>9228.93</v>
+        <v>16077.08</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>9457.52</v>
+        <v>14876.72</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
         <v>3</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>5750.09</v>
+        <v>15601.05</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>1084.8</v>
+        <v>17684.97</v>
       </c>
     </row>
     <row r="105">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C105" s="14" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D105" s="15" t="n">
-        <v>11430.7</v>
+        <v>9034.690000000001</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>12281.49</v>
+        <v>9457.52</v>
       </c>
     </row>
     <row r="106">
@@ -2990,59 +2990,59 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>15574.79</v>
+        <v>4508.91</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>16233.49</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C107" s="14" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D107" s="15" t="n">
-        <v>7055.14</v>
+        <v>14907.42</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>6867.08</v>
+        <v>12765.13</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>6914.36</v>
+        <v>20314.24</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>6995.78</v>
+        <v>17156.15</v>
       </c>
     </row>
     <row r="109">
@@ -3053,17 +3053,17 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C109" s="14" t="n">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D109" s="15" t="n">
-        <v>11336.19</v>
+        <v>6636.08</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>11998.36</v>
+        <v>6506.01</v>
       </c>
     </row>
     <row r="110">
@@ -3074,17 +3074,17 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>10881.46</v>
+        <v>7280.48</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>10096.26</v>
+        <v>7122.8</v>
       </c>
     </row>
     <row r="111">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C111" s="14" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="D111" s="15" t="n">
-        <v>16444.46</v>
+        <v>11069.58</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>8192.73</v>
+        <v>11780.05</v>
       </c>
     </row>
     <row r="112">
@@ -3116,59 +3116,59 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>20121.87</v>
+        <v>12874.05</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>18760.08</v>
+        <v>10812.45</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C113" s="14" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="D113" s="15" t="n">
-        <v>6449.19</v>
+        <v>17475.81</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>5527.77</v>
+        <v>8218.610000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>9643.620000000001</v>
+        <v>19093.92</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>8554.33</v>
+        <v>17986.99</v>
       </c>
     </row>
     <row r="115">
@@ -3179,17 +3179,17 @@
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C115" s="14" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D115" s="15" t="n">
-        <v>9904.370000000001</v>
+        <v>5797.55</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>9300.34</v>
+        <v>5212.8</v>
       </c>
     </row>
     <row r="116">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>14685.39</v>
+        <v>11581.38</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>14209.88</v>
+        <v>11431.7</v>
       </c>
     </row>
     <row r="117">
@@ -3221,59 +3221,59 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C117" s="14" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D117" s="15" t="n">
-        <v>81326.50999999999</v>
+        <v>11290.94</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>81326.50999999999</v>
+        <v>9913.6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>11309</v>
+        <v>13712.84</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>11309</v>
+        <v>13203.56</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C119" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D119" s="15" t="n">
-        <v>18539.93</v>
+        <v>24032.77</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>17181.42</v>
+        <v>24032.77</v>
       </c>
     </row>
     <row r="120">
@@ -3284,17 +3284,17 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>8946.530000000001</v>
+        <v>15452.79</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>8946.530000000001</v>
+        <v>15452.79</v>
       </c>
     </row>
     <row r="121">
@@ -3305,80 +3305,80 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C121" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D121" s="15" t="n">
-        <v>20215.57</v>
+        <v>11695.51</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>20215.57</v>
+        <v>11695.51</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>7438.13</v>
+        <v>18393.16</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>4449.86</v>
+        <v>17153.9</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C123" s="14" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D123" s="15" t="n">
-        <v>5454.6</v>
+        <v>8919</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>4638.57</v>
+        <v>8919</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>11988.92</v>
+        <v>74650.85000000001</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>12836.93</v>
+        <v>74650.85000000001</v>
       </c>
     </row>
     <row r="125">
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C125" s="14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D125" s="15" t="n">
-        <v>4898.55</v>
+        <v>5561.81</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>4898.55</v>
+        <v>4329.8</v>
       </c>
     </row>
     <row r="126">
@@ -3410,80 +3410,80 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>31073.86</v>
+        <v>7492.58</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>31073.86</v>
+        <v>4477.23</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C127" s="14" t="n">
-        <v>292</v>
+        <v>4</v>
       </c>
       <c r="D127" s="15" t="n">
-        <v>6490.6</v>
+        <v>12093.97</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>6553.81</v>
+        <v>13320.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>2583.75</v>
+        <v>5509.66</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>1084.8</v>
+        <v>5509.66</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C129" s="14" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="D129" s="15" t="n">
-        <v>9838.030000000001</v>
+        <v>20646.4</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>10165.34</v>
+        <v>20646.4</v>
       </c>
     </row>
     <row r="130">
@@ -3494,17 +3494,17 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>10847.45</v>
+        <v>6364.06</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>10403.15</v>
+        <v>6526.29</v>
       </c>
     </row>
     <row r="131">
@@ -3515,17 +3515,17 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C131" s="14" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="D131" s="15" t="n">
-        <v>14641.11</v>
+        <v>2418.98</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>13925.06</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="132">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>26-30 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>17175.73</v>
+        <v>10608.77</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>16418.6</v>
+        <v>10499.14</v>
       </c>
     </row>
     <row r="133">
@@ -3557,80 +3557,80 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C133" s="14" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="D133" s="15" t="n">
-        <v>14070.99</v>
+        <v>10351.23</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>14538.74</v>
+        <v>10493.45</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>8559</v>
+        <v>15043.77</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>5807.64</v>
+        <v>14064.28</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>26-30 anos</t>
         </is>
       </c>
       <c r="C135" s="14" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="D135" s="15" t="n">
-        <v>8312.040000000001</v>
+        <v>18279.33</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>5177.32</v>
+        <v>16571.38</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>8169.48</v>
+        <v>14287.68</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>5966.25</v>
+        <v>14524.98</v>
       </c>
     </row>
     <row r="137">
@@ -3641,17 +3641,17 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C137" s="14" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="D137" s="15" t="n">
-        <v>15395.22</v>
+        <v>7858.54</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>16310.05</v>
+        <v>5632.06</v>
       </c>
     </row>
     <row r="138">
@@ -3662,17 +3662,17 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>21-25 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>26078.65</v>
+        <v>11728.18</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>26078.65</v>
+        <v>13465.1</v>
       </c>
     </row>
     <row r="139">
@@ -3683,80 +3683,80 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>30+ anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C139" s="14" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="D139" s="15" t="n">
-        <v>13053.62</v>
+        <v>9263.34</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>9418.959999999999</v>
+        <v>6183.86</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>9821.040000000001</v>
+        <v>15485.89</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>9423.700000000001</v>
+        <v>16282.53</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>21-25 anos</t>
         </is>
       </c>
       <c r="C141" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D141" s="15" t="n">
-        <v>14958.42</v>
+        <v>25913.48</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>14958.42</v>
+        <v>25913.48</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>30+ anos</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>14244.32</v>
+        <v>10855.7</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>14244.32</v>
+        <v>9025.690000000001</v>
       </c>
     </row>
     <row r="143">
@@ -3767,80 +3767,80 @@
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C143" s="14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D143" s="15" t="n">
-        <v>15686.79</v>
+        <v>9405.610000000001</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>15686.79</v>
+        <v>9546.57</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>0-5 anos</t>
+          <t>6-10 anos</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>6866.09</v>
+        <v>15191.85</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>6430.75</v>
+        <v>15191.85</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>6-10 anos</t>
+          <t>11-15 anos</t>
         </is>
       </c>
       <c r="C145" s="14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D145" s="15" t="n">
-        <v>6999.72</v>
+        <v>12668.77</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>5889.67</v>
+        <v>12668.77</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="8" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>11-15 anos</t>
+          <t>16-20 anos</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="D146" s="11" t="n">
-        <v>11493.62</v>
+        <v>14836.92</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>11443.52</v>
+        <v>14836.92</v>
       </c>
     </row>
     <row r="147">
@@ -3851,17 +3851,17 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>16-20 anos</t>
+          <t>0-5 anos</t>
         </is>
       </c>
       <c r="C147" s="14" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D147" s="15" t="n">
-        <v>12804.11</v>
+        <v>6734.1</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>13417.31</v>
+        <v>6417.4</v>
       </c>
     </row>
     <row r="148">
@@ -3872,21 +3872,84 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
+          <t>6-10 anos</t>
+        </is>
+      </c>
+      <c r="C148" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>8212.76</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>6035.55</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>11-15 anos</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D149" s="15" t="n">
+        <v>11530.16</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>10682.28</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="8" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B150" s="9" t="inlineStr">
+        <is>
+          <t>16-20 anos</t>
+        </is>
+      </c>
+      <c r="C150" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D150" s="11" t="n">
+        <v>12528.5</v>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>13070.42</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
           <t>30+ anos</t>
         </is>
       </c>
-      <c r="C148" s="10" t="n">
+      <c r="C151" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="D148" s="11" t="n">
-        <v>21394</v>
-      </c>
-      <c r="E148" s="11" t="n">
-        <v>20966.55</v>
+      <c r="D151" s="15" t="n">
+        <v>19610.14</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>20034.09</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E148"/>
+  <autoFilter ref="A1:E151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>